--- a/data/ams_weekly_data/White_Mulberry/ads_report_week36.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week36.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -774,10 +774,10 @@
         <v>14345</v>
       </c>
       <c r="G12" t="n">
-        <v>14066.11</v>
+        <v>21099.16</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -914,10 +914,10 @@
         <v>8861</v>
       </c>
       <c r="G17" t="n">
-        <v>7287.29</v>
+        <v>14574.58</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1891,7 +1891,7 @@
         <v>111</v>
       </c>
       <c r="F52" t="n">
-        <v>13177</v>
+        <v>13176</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1104.78</v>
+        <v>1096.14</v>
       </c>
       <c r="E77" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F77" t="n">
-        <v>107759</v>
+        <v>107758</v>
       </c>
       <c r="G77" t="n">
         <v>3049.16</v>
